--- a/artfynd/A 37270-2023 artfynd.xlsx
+++ b/artfynd/A 37270-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37270-2023 artfynd.xlsx
+++ b/artfynd/A 37270-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114704479</v>
+        <v>119354186</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bageråsklacken (Bageråsklacken), Ång</t>
+          <t>Bageråsklacken, Bageråsklacken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587643</v>
+        <v>587615</v>
       </c>
       <c r="R2" t="n">
-        <v>7066596</v>
+        <v>7066562</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114704803</v>
+        <v>119354203</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,43 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bageråsklacken (Bageråsklacken), Ång</t>
+          <t>Bageråsklacken, Bageråsklacken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587579</v>
+        <v>587615</v>
       </c>
       <c r="R3" t="n">
-        <v>7066516</v>
+        <v>7066565</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114704911</v>
+        <v>119354265</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,43 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bageråsklacken (Bageråsklacken), Ång</t>
+          <t>Bageråsklacken, Bageråsklacken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587568</v>
+        <v>587591</v>
       </c>
       <c r="R4" t="n">
-        <v>7066516</v>
+        <v>7066550</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114704693</v>
+        <v>119357721</v>
       </c>
       <c r="B5" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,38 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bageråsklacken (Bageråsklacken), Ång</t>
+          <t>Bageråsklacken, Bageråsklacken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587612</v>
+        <v>587636</v>
       </c>
       <c r="R5" t="n">
-        <v>7066549</v>
+        <v>7066588</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,27 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119354186</v>
+        <v>114704693</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,37 +1084,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bageråsklacken, Bageråsklacken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587615</v>
+        <v>587612</v>
       </c>
       <c r="R6" t="n">
-        <v>7066562</v>
+        <v>7066549</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,22 +1139,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,49 +1169,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119357721</v>
+        <v>119354374</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587636</v>
+        <v>587494</v>
       </c>
       <c r="R7" t="n">
-        <v>7066588</v>
+        <v>7066473</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,9 +1249,19 @@
           <t>2024-08-26</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,65 +1276,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119354265</v>
+        <v>114704479</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bageråsklacken, Bageråsklacken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587591</v>
+        <v>587643</v>
       </c>
       <c r="R8" t="n">
-        <v>7066550</v>
+        <v>7066596</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,12 +1359,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,27 +1389,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119354203</v>
+        <v>114704803</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,37 +1412,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bageråsklacken, Bageråsklacken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587615</v>
+        <v>587579</v>
       </c>
       <c r="R9" t="n">
-        <v>7066565</v>
+        <v>7066516</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,12 +1472,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,15 +1502,128 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114704911</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bageråsklacken, Bageråsklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>587568</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7066516</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37270-2023 artfynd.xlsx
+++ b/artfynd/A 37270-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354186</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354203</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354265</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119357721</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114704693</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354374</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114704479</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114704803</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,8 +1669,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114704911</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>